--- a/order_forms/040_raw_dog_food_delivery_order_form--order_forms.xlsx
+++ b/order_forms/040_raw_dog_food_delivery_order_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_'2-1',_'name':_'delivery_day',_'label':_'delivery_day',_'value':_'wednesday',_'required':_false}</t>
+          <t>delivery_day</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': '2-1', 'name': 'delivery_day', 'label': 'Delivery Day', 'value': 'Wednesday', 'required': False}</t>
+          <t>Delivery Day</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_'2-2',_'name':_'pickup_location',_'label':_'pickup_location',_'value':_'home',_'required':_false}</t>
+          <t>pickup_location</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': '2-2', 'name': 'pickup_location', 'label': 'Pickup Location', 'value': 'Home', 'required': False}</t>
+          <t>Pickup Location</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_'3-1',_'name':_'payment_method',_'label':_'payment_method',_'value':_'credit_card',_'required':_true}</t>
+          <t>payment_method</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': '3-1', 'name': 'payment_method', 'label': 'Payment Method', 'value': 'Credit Card', 'required': True}</t>
+          <t>Payment Method</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_'3-2',_'name':_'payment_type',_'label':_'payment_type',_'value':_'one_time_payment',_'required':_false}</t>
+          <t>payment_type</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': '3-2', 'name': 'payment_type', 'label': 'Payment Type', 'value': 'One Time Payment', 'required': False}</t>
+          <t>Payment Type</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_'6-1',_'name':_'raw_food_type_1',_'label':_'chicken',_'value':_'chicken',_'required':_false}</t>
+          <t>chicken</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': '6-1', 'name': 'raw_food_type_1', 'label': 'Chicken', 'value': 'Chicken', 'required': False}</t>
+          <t>Chicken</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_'6-2',_'name':_'raw_food_type_2',_'label':_'fish',_'value':_'fish',_'required':_false}</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': '6-2', 'name': 'raw_food_type_2', 'label': 'Fish', 'value': 'Fish', 'required': False}</t>
+          <t>Fish</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_'6-3',_'name':_'beef',_'label':_'beef',_'required':_false}</t>
+          <t>beef</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': '6-3', 'name': 'beef', 'label': 'Beef', 'required': False}</t>
+          <t>Beef</t>
         </is>
       </c>
     </row>
